--- a/excel-files/LAS PINAS/MANUYO ELEMENTARY SCHOOL.xlsx
+++ b/excel-files/LAS PINAS/MANUYO ELEMENTARY SCHOOL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29711"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29816"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="127" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{36FB52ED-FE94-4134-B9D2-D0DA8EE3561A}"/>
+  <xr:revisionPtr revIDLastSave="346" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1826AFE9-842D-4742-A80F-419DF0FF09F9}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TextBooks" sheetId="1" r:id="rId1"/>
@@ -793,6 +793,9 @@
     <xf numFmtId="0" fontId="16" fillId="14" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -804,9 +807,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4150,7 +4150,7 @@
       <c r="D27" s="29">
         <v>351</v>
       </c>
-      <c r="E27" s="29">
+      <c r="E27" s="1">
         <v>2024</v>
       </c>
       <c r="F27" s="31" t="s">
@@ -4169,7 +4169,7 @@
       <c r="A28" s="1">
         <v>4</v>
       </c>
-      <c r="B28" s="50" t="s">
+      <c r="B28" s="46" t="s">
         <v>19</v>
       </c>
       <c r="C28" s="1">
@@ -4193,7 +4193,7 @@
       <c r="A29" s="1">
         <v>4</v>
       </c>
-      <c r="B29" s="50" t="s">
+      <c r="B29" s="46" t="s">
         <v>20</v>
       </c>
       <c r="C29" s="1">
@@ -5613,16 +5613,19 @@
     </row>
   </sheetData>
   <protectedRanges>
-    <protectedRange sqref="C1:E98" name="Textbooks"/>
-    <protectedRange sqref="F1:F98" name="SOURCE"/>
+    <protectedRange sqref="F28 C1:E98" name="Textbooks"/>
+    <protectedRange sqref="F1:F27 F29:F98" name="SOURCE"/>
   </protectedRanges>
   <phoneticPr fontId="8" type="noConversion"/>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E14:E19 E91:E98 E31:E39 E51:E59 E61:E69 E41:E49 E2:E6 E71:E79 E81:E89 E8:E12 E21:E29" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F28" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
       <formula1>"2024,2025"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F21:F29 F31:F39 F41:F49 F51:F59 F61:F69 F71:F79 F81:F89 F2:F6 F8:F12 F91:F98" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F91:F98 F31:F39 F41:F49 F51:F59 F61:F69 F71:F79 F81:F89 F2:F6 F8:F12 F21:F27 F29" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
       <formula1>"CO,RO,SDO"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E41:E49 E8:E12 E2:E6 E14:E19 E21:E29 E31:E39 E51:E59 E61:E69 E71:E79 E81:E89 E91:E98" xr:uid="{A2966CE6-6935-4859-B1F0-CCAF1D0E6993}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5634,7 +5637,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0858F8C8-8AF8-4852-B88C-61047AF726C8}">
-  <dimension ref="A1:AA157"/>
+  <dimension ref="A1:AA127"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -5664,38 +5667,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1">
-      <c r="D1" s="46" t="s">
+      <c r="D1" s="47" t="s">
         <v>33</v>
       </c>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
-      <c r="G1" s="46"/>
-      <c r="H1" s="46"/>
-      <c r="I1" s="46"/>
-      <c r="J1" s="47" t="s">
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="47"/>
+      <c r="J1" s="48" t="s">
         <v>34</v>
       </c>
-      <c r="K1" s="47"/>
-      <c r="L1" s="47"/>
-      <c r="M1" s="47"/>
-      <c r="N1" s="47"/>
-      <c r="O1" s="47"/>
-      <c r="P1" s="48" t="s">
+      <c r="K1" s="48"/>
+      <c r="L1" s="48"/>
+      <c r="M1" s="48"/>
+      <c r="N1" s="48"/>
+      <c r="O1" s="48"/>
+      <c r="P1" s="49" t="s">
         <v>35</v>
       </c>
-      <c r="Q1" s="48"/>
-      <c r="R1" s="48"/>
-      <c r="S1" s="48"/>
-      <c r="T1" s="48"/>
-      <c r="U1" s="48"/>
-      <c r="V1" s="49" t="s">
+      <c r="Q1" s="49"/>
+      <c r="R1" s="49"/>
+      <c r="S1" s="49"/>
+      <c r="T1" s="49"/>
+      <c r="U1" s="49"/>
+      <c r="V1" s="50" t="s">
         <v>36</v>
       </c>
-      <c r="W1" s="49"/>
-      <c r="X1" s="49"/>
-      <c r="Y1" s="49"/>
-      <c r="Z1" s="49"/>
-      <c r="AA1" s="49"/>
+      <c r="W1" s="50"/>
+      <c r="X1" s="50"/>
+      <c r="Y1" s="50"/>
+      <c r="Z1" s="50"/>
+      <c r="AA1" s="50"/>
     </row>
     <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1">
       <c r="A2" s="15" t="s">
@@ -10057,7 +10060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:27" ht="19.149999999999999">
+    <row r="64" spans="1:27" ht="19.5">
       <c r="A64" s="10">
         <v>7</v>
       </c>
@@ -10126,7 +10129,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:27" ht="19.149999999999999">
+    <row r="65" spans="1:27" ht="19.5">
       <c r="A65" s="10">
         <v>7</v>
       </c>
@@ -10195,7 +10198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:27" ht="19.149999999999999">
+    <row r="66" spans="1:27" ht="19.5">
       <c r="A66" s="10">
         <v>7</v>
       </c>
@@ -10264,7 +10267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:27" ht="19.149999999999999">
+    <row r="67" spans="1:27" ht="38.25">
       <c r="A67" s="10">
         <v>7</v>
       </c>
@@ -10333,7 +10336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:27" ht="19.149999999999999">
+    <row r="68" spans="1:27" ht="19.5">
       <c r="A68" s="10">
         <v>7</v>
       </c>
@@ -10402,7 +10405,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:27" ht="19.149999999999999">
+    <row r="69" spans="1:27" ht="19.5">
       <c r="A69" s="10">
         <v>7</v>
       </c>
@@ -10471,7 +10474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:27" ht="19.149999999999999">
+    <row r="70" spans="1:27" ht="19.5">
       <c r="A70" s="10">
         <v>7</v>
       </c>
@@ -10540,7 +10543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:27" ht="19.149999999999999">
+    <row r="71" spans="1:27" ht="19.5">
       <c r="A71" s="10">
         <v>7</v>
       </c>
@@ -10692,7 +10695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:27" ht="19.149999999999999">
+    <row r="74" spans="1:27" ht="19.5">
       <c r="A74" s="10">
         <v>8</v>
       </c>
@@ -10761,7 +10764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:27" ht="19.149999999999999">
+    <row r="75" spans="1:27" ht="19.5">
       <c r="A75" s="10">
         <v>8</v>
       </c>
@@ -10830,7 +10833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:27" ht="19.149999999999999">
+    <row r="76" spans="1:27" ht="19.5">
       <c r="A76" s="10">
         <v>8</v>
       </c>
@@ -10899,7 +10902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:27" ht="19.149999999999999">
+    <row r="77" spans="1:27" ht="19.5">
       <c r="A77" s="10">
         <v>8</v>
       </c>
@@ -10968,7 +10971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:27" ht="19.149999999999999">
+    <row r="78" spans="1:27" ht="19.5">
       <c r="A78" s="10">
         <v>8</v>
       </c>
@@ -11037,7 +11040,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:27" ht="19.149999999999999">
+    <row r="79" spans="1:27" ht="19.5">
       <c r="A79" s="10">
         <v>8</v>
       </c>
@@ -11106,7 +11109,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:27" ht="19.149999999999999">
+    <row r="80" spans="1:27" ht="19.5">
       <c r="A80" s="10">
         <v>8</v>
       </c>
@@ -11175,7 +11178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:27" ht="19.149999999999999">
+    <row r="81" spans="1:27" ht="19.5">
       <c r="A81" s="10">
         <v>8</v>
       </c>
@@ -11244,7 +11247,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="82" spans="1:27" s="7" customFormat="1" ht="19.5">
       <c r="J82" s="13"/>
       <c r="M82" s="5"/>
       <c r="N82" s="13"/>
@@ -11327,7 +11330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:27" ht="19.149999999999999">
+    <row r="84" spans="1:27" ht="19.5">
       <c r="A84" s="10">
         <v>9</v>
       </c>
@@ -11396,7 +11399,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:27" ht="19.149999999999999">
+    <row r="85" spans="1:27" ht="19.5">
       <c r="A85" s="10">
         <v>9</v>
       </c>
@@ -11465,7 +11468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:27" ht="19.149999999999999">
+    <row r="86" spans="1:27" ht="19.5">
       <c r="A86" s="10">
         <v>9</v>
       </c>
@@ -11534,7 +11537,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:27" ht="19.149999999999999">
+    <row r="87" spans="1:27" ht="19.5">
       <c r="A87" s="10">
         <v>9</v>
       </c>
@@ -11603,7 +11606,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:27" ht="19.149999999999999">
+    <row r="88" spans="1:27" ht="19.5">
       <c r="A88" s="10">
         <v>9</v>
       </c>
@@ -11672,7 +11675,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:27" ht="19.149999999999999">
+    <row r="89" spans="1:27" ht="19.5">
       <c r="A89" s="10">
         <v>9</v>
       </c>
@@ -11741,7 +11744,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:27" ht="19.149999999999999">
+    <row r="90" spans="1:27" ht="19.5">
       <c r="A90" s="10">
         <v>9</v>
       </c>
@@ -11810,7 +11813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:27" ht="19.149999999999999">
+    <row r="91" spans="1:27" ht="19.5">
       <c r="A91" s="10">
         <v>9</v>
       </c>
@@ -11962,7 +11965,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:27" ht="19.149999999999999">
+    <row r="94" spans="1:27" ht="19.5">
       <c r="A94" s="10">
         <v>10</v>
       </c>
@@ -12031,7 +12034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:27" ht="19.149999999999999">
+    <row r="95" spans="1:27" ht="19.5">
       <c r="A95" s="10">
         <v>10</v>
       </c>
@@ -12100,7 +12103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:27" ht="19.149999999999999">
+    <row r="96" spans="1:27" ht="19.5">
       <c r="A96" s="10">
         <v>10</v>
       </c>
@@ -12169,7 +12172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:27" ht="19.149999999999999">
+    <row r="97" spans="1:27" ht="19.5">
       <c r="A97" s="10">
         <v>10</v>
       </c>
@@ -12238,7 +12241,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:27" ht="19.149999999999999">
+    <row r="98" spans="1:27" ht="19.5">
       <c r="A98" s="10">
         <v>10</v>
       </c>
@@ -12307,7 +12310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:27" ht="19.149999999999999">
+    <row r="99" spans="1:27" ht="19.5">
       <c r="A99" s="10">
         <v>10</v>
       </c>
@@ -12376,7 +12379,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:27" ht="19.149999999999999">
+    <row r="100" spans="1:27" ht="19.5">
       <c r="A100" s="10">
         <v>10</v>
       </c>
@@ -12445,7 +12448,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:27" ht="19.149999999999999">
+    <row r="101" spans="1:27" ht="19.5">
       <c r="A101" s="10">
         <v>10</v>
       </c>
@@ -12528,7 +12531,7 @@
       <c r="Z102" s="13"/>
       <c r="AA102" s="13"/>
     </row>
-    <row r="103" spans="1:27" ht="38.450000000000003">
+    <row r="103" spans="1:27" ht="38.25">
       <c r="A103" s="1" t="s">
         <v>24</v>
       </c>
@@ -12597,7 +12600,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:27" ht="19.149999999999999">
+    <row r="104" spans="1:27" ht="19.5">
       <c r="A104" s="1" t="s">
         <v>24</v>
       </c>
@@ -12666,7 +12669,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:27" ht="19.149999999999999">
+    <row r="105" spans="1:27" ht="19.5">
       <c r="A105" s="1" t="s">
         <v>24</v>
       </c>
@@ -12735,7 +12738,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:27" ht="19.149999999999999">
+    <row r="106" spans="1:27" ht="19.5">
       <c r="A106" s="1" t="s">
         <v>24</v>
       </c>
@@ -12804,7 +12807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:27" ht="38.450000000000003">
+    <row r="107" spans="1:27" ht="38.25">
       <c r="A107" s="1" t="s">
         <v>24</v>
       </c>
@@ -12873,7 +12876,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:27" ht="19.149999999999999">
+    <row r="108" spans="1:27" ht="38.25">
       <c r="A108" s="1" t="s">
         <v>24</v>
       </c>
@@ -12942,7 +12945,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:27" ht="38.450000000000003">
+    <row r="109" spans="1:27" ht="57.75">
       <c r="A109" s="1" t="s">
         <v>24</v>
       </c>
@@ -13011,7 +13014,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:27" ht="38.450000000000003">
+    <row r="110" spans="1:27" ht="38.25">
       <c r="A110" s="1" t="s">
         <v>24</v>
       </c>
@@ -13153,7 +13156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:27" ht="19.149999999999999">
+    <row r="113" spans="1:27" ht="19.5">
       <c r="A113" s="1"/>
       <c r="B113" s="9"/>
       <c r="C113" s="1"/>
@@ -13215,7 +13218,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:27" ht="19.149999999999999">
+    <row r="114" spans="1:27" ht="19.5">
       <c r="A114" s="1"/>
       <c r="B114" s="9"/>
       <c r="C114" s="1"/>
@@ -13277,7 +13280,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:27" ht="19.149999999999999">
+    <row r="115" spans="1:27" ht="19.5">
       <c r="A115" s="1"/>
       <c r="B115" s="9"/>
       <c r="C115" s="1"/>
@@ -13339,7 +13342,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:27" ht="19.149999999999999">
+    <row r="116" spans="1:27" ht="19.5">
       <c r="A116" s="1"/>
       <c r="B116" s="9"/>
       <c r="C116" s="1"/>
@@ -13401,7 +13404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:27" ht="19.149999999999999">
+    <row r="117" spans="1:27" ht="19.5">
       <c r="A117" s="1"/>
       <c r="B117" s="9"/>
       <c r="C117" s="1"/>
@@ -13463,7 +13466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:27" ht="19.149999999999999">
+    <row r="118" spans="1:27" ht="19.5">
       <c r="A118" s="1"/>
       <c r="B118" s="9"/>
       <c r="C118" s="1"/>
@@ -13525,7 +13528,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:27" ht="19.149999999999999">
+    <row r="119" spans="1:27" ht="19.5">
       <c r="A119" s="1"/>
       <c r="B119" s="9"/>
       <c r="C119" s="1"/>
@@ -13587,7 +13590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:27" ht="19.149999999999999">
+    <row r="120" spans="1:27" ht="19.5">
       <c r="A120" s="1"/>
       <c r="B120" s="9"/>
       <c r="C120" s="1"/>
@@ -13649,7 +13652,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:27" ht="19.149999999999999">
+    <row r="121" spans="1:27" ht="19.5">
       <c r="A121" s="1"/>
       <c r="B121" s="9"/>
       <c r="C121" s="1"/>
@@ -13711,7 +13714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:27" ht="19.149999999999999">
+    <row r="122" spans="1:27" ht="19.5">
       <c r="A122" s="1"/>
       <c r="B122" s="9"/>
       <c r="C122" s="1"/>
@@ -13773,7 +13776,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:27" ht="19.149999999999999">
+    <row r="123" spans="1:27" ht="19.5">
       <c r="A123" s="1"/>
       <c r="B123" s="9"/>
       <c r="C123" s="1"/>
@@ -13835,7 +13838,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:27" ht="19.149999999999999">
+    <row r="124" spans="1:27" ht="19.5">
       <c r="A124" s="1"/>
       <c r="B124" s="9"/>
       <c r="C124" s="1"/>
@@ -13897,7 +13900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:27" ht="19.149999999999999">
+    <row r="125" spans="1:27" ht="19.5">
       <c r="A125" s="1"/>
       <c r="B125" s="9"/>
       <c r="C125" s="1"/>
@@ -13959,7 +13962,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:27" ht="19.149999999999999">
+    <row r="126" spans="1:27" ht="19.5">
       <c r="A126" s="1"/>
       <c r="B126" s="9"/>
       <c r="C126" s="1"/>
@@ -14021,13 +14024,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:27" ht="19.149999999999999">
+    <row r="127" spans="1:27" ht="19.5">
       <c r="A127" s="29"/>
       <c r="B127" s="30"/>
       <c r="C127" s="29"/>
       <c r="D127" s="5"/>
       <c r="E127" s="31"/>
-      <c r="F127" s="29"/>
+      <c r="F127" s="1"/>
       <c r="G127" s="31"/>
       <c r="H127" s="5">
         <f t="shared" si="22"/>
@@ -14042,7 +14045,7 @@
         <v>0</v>
       </c>
       <c r="K127" s="31"/>
-      <c r="L127" s="29"/>
+      <c r="L127" s="1"/>
       <c r="M127" s="31"/>
       <c r="N127" s="5">
         <f t="shared" ref="N127" si="24">IF((J127-K127)&lt;0,0,(J127-K127))</f>
@@ -14054,7 +14057,7 @@
       </c>
       <c r="P127" s="5"/>
       <c r="Q127" s="31"/>
-      <c r="R127" s="29"/>
+      <c r="R127" s="1"/>
       <c r="S127" s="31"/>
       <c r="T127" s="5">
         <f t="shared" si="18"/>
@@ -14069,7 +14072,7 @@
         <v>0</v>
       </c>
       <c r="W127" s="31"/>
-      <c r="X127" s="29"/>
+      <c r="X127" s="1"/>
       <c r="Y127" s="31"/>
       <c r="Z127" s="5">
         <f t="shared" si="20"/>
@@ -14080,190 +14083,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:27">
-      <c r="J128" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="129" spans="10:10">
-      <c r="J129" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="130" spans="10:10">
-      <c r="J130" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="131" spans="10:10">
-      <c r="J131" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="132" spans="10:10">
-      <c r="J132" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="133" spans="10:10">
-      <c r="J133" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="134" spans="10:10">
-      <c r="J134" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="135" spans="10:10">
-      <c r="J135" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="136" spans="10:10">
-      <c r="J136" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="137" spans="10:10">
-      <c r="J137" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="138" spans="10:10">
-      <c r="J138" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="139" spans="10:10">
-      <c r="J139" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="140" spans="10:10">
-      <c r="J140" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="141" spans="10:10">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="10:10">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="10:10">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="10:10">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C2:C3 C14:C21 C23:C31 C33:C41 C43:C51 C53:C61 C63:C71 C73:C81 C83:C91 C93:C101 C103:C110 C112:C127 C5:C12" name="Textbooks"/>
-    <protectedRange sqref="J2:L3 D2:F3 H5:J5 Q14:R21 W14:X21 Q23:R31 W23:X31 H33:I41 Q33:R41 W33:X41 H43:I51 Q43:R51 W43:X51 H53:I61 Q53:R61 W53:X61 D63:F71 H63:I71 Q63:R71 W63:X71 D73:F81 H73:I81 Q73:R81 W73:X81 D83:F91 H83:I91 Q83:R91 W83:X91 D93:F101 H93:I101 Q93:R101 W93:X101 D103:F110 H103:I110 Q103:R110 W103:X110 D112:F127 H112:I127 N127:R127 W112:X127 H14:I21 H23:I31 H6:I12 K63:L71 K73:L81 K83:L91 K93:L101 K103:L110 K112:L127 Q112:R126 P2:R2 V2:X3 N13:P126 T13:V127 J6:J127 N5:R12 T5:X12 N4:P4 T4:V4 J4 Z4:AA127 N3:R3 Y13 D5:F12 D14:F21 D23:F31 D33:F41 D43:F51 D53:F61 K5:L12 K14:L21 K23:L31 K33:L41 K43:L51 K53:L61" name="LAS"/>
+    <protectedRange sqref="J2:L3 D2:F3 H5:J5 H33:I41 H43:I51 H53:I61 H63:I71 W63:X71 H73:I81 H83:I91 H93:I101 H103:I110 H112:I127 N127:Q127 H14:I21 H23:I31 H6:I12 Q112:R112 P2:R2 V2:X3 N13:P126 T13:V127 J6:J127 N4:P4 T4:V4 J4 Z4:AA127 N3:R3 Y13 D5:F12 D14:F21 D23:F31 D33:F41 D43:F51 D53:F61 D63:F71 D73:F81 D83:F91 D93:F101 D103:F110 D112:F127 K5:L12 K14:L21 K23:L31 K33:L41 K43:L51 K53:L61 K63:L71 K73:L81 K83:L91 K93:L101 K103:L110 K112:L127 N5:R12 Q14:R21 Q23:R31 Q33:R41 Q43:R51 Q53:R61 Q63:R71 Q73:R81 Q83:R91 Q93:R101 Q103:R110 Q113:Q126 R113:R127 T5:X12 W14:X21 W23:X31 W33:X41 W43:X51 W53:X61 W73:X81 W83:X91 W93:X101 W103:X110 W112:X127" name="LAS"/>
     <protectedRange sqref="G2:I3 M2:O2 S2:U3 Y2:AA3 G112:G127 M112:M127 S112:S127 Y112:Y127 G5:G12 M5:M12 S4:S110 Y5:Y12 G14:G21 M14:M110 M3 Y14:Y110 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110" name="SOURCE"/>
   </protectedRanges>
   <dataConsolidate/>
@@ -14273,15 +14096,21 @@
     <mergeCell ref="P1:U1"/>
     <mergeCell ref="V1:AA1"/>
   </mergeCells>
-  <dataValidations count="3">
+  <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S112:S127 M112:M127 Y112:Y127 G112:G127" xr:uid="{8289B4A9-982E-4C7E-A8E2-4BF3404561DB}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X23:X31 X33:X41 X43:X51 X63:X71 X73:X81 X53:X61 L112:L127 X83:X91 X93:X101 X14:X21 X5:X12 L14:L21 L23:L31 L33:L41 L63:L71 L73:L81 L43:L51 R112:R127 L83:L91 L93:L101 L5:L12 F53:F61 R23:R31 R33:R41 R43:R51 R63:R71 R73:R81 R53:R61 F112:F127 R83:R91 R93:R101 R14:R21 R5:R12 F14:F21 F23:F31 F33:F41 F63:F71 F73:F81 F43:F51 X112:X127 F83:F91 F93:F101 F5:F12 F103:F110 R103:R110 L103:L110 X103:X110 L53:L61" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X112:X127" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M14:M110 Y14:Y110 S4:S110 G5:G12 M5:M12 Y5:Y12 G14:G21 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F5:F12 F14:F21 F23:F31 F33:F41 F43:F51 F53:F61 F63:F71 F73:F81 F83:F91 F93:F101 F103:F110 F112:F127 L5:L12 L14:L21 L23:L31 L33:L41 L43:L51 L53:L61 L63:L71 L73:L81 L83:L91" xr:uid="{D5F6913F-60E7-4083-A9D7-1267B76C477F}">
+      <formula1>"2024,2025,2026"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L93:L101 L103:L110 L112:L127 R5:R12 R14:R21 R23:R31 R33:R41 R43:R61 R63:R71 R73:R81 R83:R91 R93:R101 R103:R110 R112:R127 X5:X12 X14:X21 X23:X31 X33:X41 X43:X51 X53:X61 X63:X71 X73:X81 X83:X91 X93:X101 X103:X110" xr:uid="{9C6AA934-C4DD-48C4-80CA-41EABD4DF187}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14296,7 +14125,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F176E3C0-9A94-45E4-9AFD-70DF8ABE5E5A}">
-  <dimension ref="A1:AB170"/>
+  <dimension ref="A1:AB141"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -14326,38 +14155,38 @@
   <sheetData>
     <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1">
       <c r="B1" s="35"/>
-      <c r="D1" s="46" t="s">
+      <c r="D1" s="47" t="s">
         <v>33</v>
       </c>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
-      <c r="G1" s="46"/>
-      <c r="H1" s="46"/>
-      <c r="I1" s="46"/>
-      <c r="J1" s="47" t="s">
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="47"/>
+      <c r="J1" s="48" t="s">
         <v>34</v>
       </c>
-      <c r="K1" s="47"/>
-      <c r="L1" s="47"/>
-      <c r="M1" s="47"/>
-      <c r="N1" s="47"/>
-      <c r="O1" s="47"/>
-      <c r="P1" s="48" t="s">
+      <c r="K1" s="48"/>
+      <c r="L1" s="48"/>
+      <c r="M1" s="48"/>
+      <c r="N1" s="48"/>
+      <c r="O1" s="48"/>
+      <c r="P1" s="49" t="s">
         <v>35</v>
       </c>
-      <c r="Q1" s="48"/>
-      <c r="R1" s="48"/>
-      <c r="S1" s="48"/>
-      <c r="T1" s="48"/>
-      <c r="U1" s="48"/>
-      <c r="V1" s="49" t="s">
+      <c r="Q1" s="49"/>
+      <c r="R1" s="49"/>
+      <c r="S1" s="49"/>
+      <c r="T1" s="49"/>
+      <c r="U1" s="49"/>
+      <c r="V1" s="50" t="s">
         <v>36</v>
       </c>
-      <c r="W1" s="49"/>
-      <c r="X1" s="49"/>
-      <c r="Y1" s="49"/>
-      <c r="Z1" s="49"/>
-      <c r="AA1" s="49"/>
+      <c r="W1" s="50"/>
+      <c r="X1" s="50"/>
+      <c r="Y1" s="50"/>
+      <c r="Z1" s="50"/>
+      <c r="AA1" s="50"/>
     </row>
     <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1">
       <c r="A2" s="15" t="s">
@@ -14511,7 +14340,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="19.149999999999999">
+    <row r="4" spans="1:27" ht="19.5">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -14580,7 +14409,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="19.149999999999999">
+    <row r="5" spans="1:27" ht="19.5">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -14649,7 +14478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="19.149999999999999">
+    <row r="6" spans="1:27" ht="19.5">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -14718,7 +14547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="19.149999999999999">
+    <row r="7" spans="1:27" ht="19.5">
       <c r="A7" s="1">
         <v>1</v>
       </c>
@@ -14787,7 +14616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="19.149999999999999">
+    <row r="8" spans="1:27" ht="19.5">
       <c r="A8" s="1">
         <v>1</v>
       </c>
@@ -14856,7 +14685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="19.149999999999999">
+    <row r="9" spans="1:27" ht="19.5">
       <c r="A9" s="1">
         <v>1</v>
       </c>
@@ -14925,7 +14754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="19.149999999999999">
+    <row r="10" spans="1:27" ht="19.5">
       <c r="A10" s="1">
         <v>1</v>
       </c>
@@ -15064,7 +14893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="19.149999999999999">
+    <row r="13" spans="1:27" ht="19.5">
       <c r="A13" s="1">
         <v>2</v>
       </c>
@@ -15133,7 +14962,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="19.149999999999999">
+    <row r="14" spans="1:27" ht="19.5">
       <c r="A14" s="1">
         <v>2</v>
       </c>
@@ -15202,7 +15031,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="19.149999999999999">
+    <row r="15" spans="1:27" ht="19.5">
       <c r="A15" s="1">
         <v>2</v>
       </c>
@@ -15271,7 +15100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="19.149999999999999">
+    <row r="16" spans="1:27" ht="19.5">
       <c r="A16" s="1">
         <v>2</v>
       </c>
@@ -15340,7 +15169,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="19.149999999999999">
+    <row r="17" spans="1:27" ht="19.5">
       <c r="A17" s="1">
         <v>2</v>
       </c>
@@ -15409,7 +15238,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="19.149999999999999">
+    <row r="18" spans="1:27" ht="19.5">
       <c r="A18" s="1">
         <v>2</v>
       </c>
@@ -15478,7 +15307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="19.149999999999999">
+    <row r="19" spans="1:27" ht="19.5">
       <c r="A19" s="1">
         <v>2</v>
       </c>
@@ -15617,7 +15446,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="19.149999999999999">
+    <row r="22" spans="1:27" ht="19.5">
       <c r="A22" s="1">
         <v>3</v>
       </c>
@@ -15686,7 +15515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="19.149999999999999">
+    <row r="23" spans="1:27" ht="19.5">
       <c r="A23" s="1">
         <v>3</v>
       </c>
@@ -15755,7 +15584,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="19.149999999999999">
+    <row r="24" spans="1:27" ht="19.5">
       <c r="A24" s="1">
         <v>3</v>
       </c>
@@ -15824,7 +15653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="19.149999999999999">
+    <row r="25" spans="1:27" ht="19.5">
       <c r="A25" s="1">
         <v>3</v>
       </c>
@@ -15893,7 +15722,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="19.149999999999999">
+    <row r="26" spans="1:27" ht="19.5">
       <c r="A26" s="1">
         <v>3</v>
       </c>
@@ -15962,7 +15791,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="19.149999999999999">
+    <row r="27" spans="1:27" ht="19.5">
       <c r="A27" s="1">
         <v>3</v>
       </c>
@@ -16031,7 +15860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="19.149999999999999">
+    <row r="28" spans="1:27" ht="19.5">
       <c r="A28" s="1">
         <v>3</v>
       </c>
@@ -16100,7 +15929,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="19.149999999999999">
+    <row r="29" spans="1:27" ht="19.5">
       <c r="A29" s="1">
         <v>3</v>
       </c>
@@ -16239,7 +16068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:27" ht="19.149999999999999">
+    <row r="32" spans="1:27" ht="19.5">
       <c r="A32" s="1">
         <v>4</v>
       </c>
@@ -16308,7 +16137,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:27" ht="19.149999999999999">
+    <row r="33" spans="1:27" ht="19.5">
       <c r="A33" s="1">
         <v>4</v>
       </c>
@@ -16377,7 +16206,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="19.149999999999999">
+    <row r="34" spans="1:27" ht="19.5">
       <c r="A34" s="1">
         <v>4</v>
       </c>
@@ -16515,7 +16344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="19.149999999999999">
+    <row r="36" spans="1:27" ht="19.5">
       <c r="A36" s="1">
         <v>4</v>
       </c>
@@ -16584,7 +16413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="19.149999999999999">
+    <row r="37" spans="1:27" ht="19.5">
       <c r="A37" s="37">
         <v>4</v>
       </c>
@@ -16653,7 +16482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="19.149999999999999">
+    <row r="38" spans="1:27" ht="19.5">
       <c r="A38" s="1">
         <v>4</v>
       </c>
@@ -16722,7 +16551,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="19.149999999999999">
+    <row r="39" spans="1:27" ht="19.5">
       <c r="A39" s="1">
         <v>4</v>
       </c>
@@ -16791,7 +16620,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="19.149999999999999">
+    <row r="40" spans="1:27" ht="19.5">
       <c r="A40" s="37">
         <v>4</v>
       </c>
@@ -16860,7 +16689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="19.149999999999999">
+    <row r="41" spans="1:27" ht="19.5">
       <c r="A41" s="1">
         <v>4</v>
       </c>
@@ -16999,7 +16828,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="19.149999999999999">
+    <row r="44" spans="1:27" ht="19.5">
       <c r="A44" s="1">
         <v>5</v>
       </c>
@@ -17690,7 +17519,7 @@
       </c>
     </row>
     <row r="54" spans="1:27" s="7" customFormat="1"/>
-    <row r="55" spans="1:27" ht="19.149999999999999">
+    <row r="55" spans="1:27" ht="19.5">
       <c r="A55" s="1">
         <v>6</v>
       </c>
@@ -20730,7 +20559,7 @@
       </c>
     </row>
     <row r="102" spans="1:27" s="7" customFormat="1"/>
-    <row r="103" spans="1:27" ht="19.149999999999999">
+    <row r="103" spans="1:27" ht="19.5">
       <c r="A103" s="10">
         <v>10</v>
       </c>
@@ -21490,7 +21319,7 @@
       </c>
     </row>
     <row r="114" spans="1:28" s="7" customFormat="1"/>
-    <row r="115" spans="1:28" ht="38.450000000000003">
+    <row r="115" spans="1:28" ht="38.25">
       <c r="A115" s="1" t="s">
         <v>24</v>
       </c>
@@ -21628,7 +21457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:28" ht="19.149999999999999">
+    <row r="117" spans="1:28" ht="19.5">
       <c r="A117" s="1" t="s">
         <v>24</v>
       </c>
@@ -22553,190 +22382,11 @@
       <c r="AA140" s="7"/>
       <c r="AB140" s="7"/>
     </row>
-    <row r="141" spans="1:28">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="1:28">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="1:28">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="1:28">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="158" spans="10:10">
-      <c r="J158" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="159" spans="10:10">
-      <c r="J159" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="160" spans="10:10">
-      <c r="J160" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="161" spans="10:10">
-      <c r="J161" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="162" spans="10:10">
-      <c r="J162" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="163" spans="10:10">
-      <c r="J163" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="164" spans="10:10">
-      <c r="J164" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="165" spans="10:10">
-      <c r="J165" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="166" spans="10:10">
-      <c r="J166" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="167" spans="10:10">
-      <c r="J167" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="168" spans="10:10">
-      <c r="J168" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="169" spans="10:10">
-      <c r="J169" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="170" spans="10:10">
-      <c r="J170" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
+    <row r="141" spans="1:28" ht="15"/>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C2:C10 C12:C19 C21:C29 C31:C41 C43:C53 C55:C65 C67:C77 C79:C89 C115:C122 C103:C113 C91:C101" name="Textbooks"/>
-    <protectedRange sqref="J2:L2 D2:F10 D12:F19 D21:F29 D31:F41 D43:F53 D55:F65 D67:F77 D79:F89 D91:F101 D115:F122 P2:R10 N3:O10 V2:X10 T3:U10 N12:R19 T12:X19 H3:L10 Z3:AA10 Z12:AA19 H12:L19 N21:R29 T21:X29 Z21:AA29 H21:L29 T31:X41 Z31:AA41 H31:L41 T43:X53 Z43:AA53 H43:L53 T55:X65 Z55:AA65 H55:L65 T67:X77 Z67:AA77 H67:L77 T79:X89 Z79:AA89 H79:L89 T91:X101 Z91:AA101 H91:L101 T103:X113 Z103:AA113 H103:L113 N115:R122 T115:X122 Z115:AA122 H115:L122 D103:F113 N31:R41 N43:R53 N55:R65 N67:R77 N79:R89 N91:R101 N103:R113" name="LAS"/>
+    <protectedRange sqref="J2:L2 D21:F29 D31:F41 D43:F53 D55:F65 D67:F77 D79:F89 D91:F101 D115:F122 P2:R10 N3:O10 V2:X10 T3:U10 N12:R19 T12:X19 Z3:AA10 Z12:AA19 N21:R29 T21:X29 Z21:AA29 T31:X41 Z31:AA41 T43:X53 Z43:AA53 H43:L53 T55:X65 Z55:AA65 H55:L65 T67:X77 Z67:AA77 H67:L77 T79:X89 Z79:AA89 H79:L89 T91:X101 Z91:AA101 H91:L101 T103:X113 Z103:AA113 H103:L113 N115:R122 T115:X122 Z115:AA122 H115:L122 D103:F113 N31:R41 N43:R53 N55:R65 N67:R77 N79:R89 N91:R101 N103:R113 D2:F10 D12:F19 H3:L10 H12:L19 H21:L29 H31:L41" name="LAS"/>
     <protectedRange sqref="G2:I2 M2:O2 S2:U2 Y2:AA2 G3:G10 M3:M10 S3:S10 Y3:Y10 Y12:Y19 G12:G19 M12:M19 S12:S19 Y21:Y29 G21:G29 M21:M29 S21:S29 Y31:Y41 G31:G41 M31:M41 S31:S41 Y43:Y53 G43:G53 M43:M53 S43:S53 Y55:Y65 G55:G65 M55:M65 S55:S65 Y67:Y77 G67:G77 M67:M77 S67:S77 Y79:Y89 G79:G89 M79:M89 S79:S89 Y91:Y101 G91:G101 M91:M101 S91:S101 Y103:Y113 G103:G113 M103:M113 S103:S113 Y115:Y122 G115:G122 M115:M122 S115:S122" name="SOURCE"/>
   </protectedRanges>
   <dataConsolidate/>
@@ -22746,12 +22396,15 @@
     <mergeCell ref="P1:U1"/>
     <mergeCell ref="V1:AA1"/>
   </mergeCells>
-  <dataValidations count="2">
+  <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S115:S122 Y115:Y122 G115:G122 Y3:Y10 S3:S10 M3:M10 G3:G10 G12:G19 Y12:Y19 S12:S19 M12:M19 M21:M29 G21:G29 Y21:Y29 S21:S29 S31:S41 M31:M41 G31:G41 Y31:Y41 Y43:Y53 S43:S53 M43:M53 G43:G53 G55:G65 Y55:Y65 S55:S65 M55:M65 M67:M77 G67:G77 Y67:Y77 S67:S77 S79:S89 M79:M89 G79:G89 Y79:Y89 Y91:Y101 S91:S101 M91:M101 G91:G101 G103:G113 Y103:Y113 S103:S113 M103:M113 M115:M122" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X21:X29 X31:X41 X43:X53 X67:X77 X79:X89 X55:X65 X91:X101 X103:X113 X12:X19 X3:X10 L21:L29 L31:L41 L43:L53 L67:L77 L79:L89 L55:L65 L91:L101 L103:L113 L12:L19 L3:L10 R21:R29 R31:R41 R43:R53 R67:R77 R79:R89 R55:R65 R91:R101 R103:R113 R12:R19 R3:R10 F21:F29 F31:F41 F43:F53 F67:F77 F79:F89 F55:F65 F3:F10 F91:F101 X115:X122 F12:F19 F115:F122 R115:R122 L115:L122 F103:F113" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X115:X122" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
+      <formula1>"2024,2025,2026"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F10 F12:F19 F21:F29 F31:F41 F43:F53 F55:F65 F67:F77 F79:F89 F91:F101 F103:F113 F115:F122 L3:L10 L12:L19 L21:L29 L31:L41 L43:L53 L55:L65 L67:L77 L79:L89 L91:L101 L103:L113 L115:L122 R3:R10 R12:R19 R21:R29 R31:R41 R43:R53 R55:R65 R67:R77 R79:R89 R91:R101 R103:R113 R115:R122 X3:X10 X12:X19 X21:X29 X31:X41 X43:X53 X55:X65 X67:X77 X79:X89 X91:X101 X103:X113" xr:uid="{03AB6873-2935-4483-96C9-A6711FB80AFD}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
